--- a/data/stx_xlsx/AFRY.ST.xlsx
+++ b/data/stx_xlsx/AFRY.ST.xlsx
@@ -14992,22 +14992,50 @@
       <c r="H86" s="16">
         <v>220.35</v>
       </c>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
+      <c r="I86" s="15">
+        <f>SUM(I87:I89)</f>
+        <v>640.16</v>
+      </c>
+      <c r="J86" s="15">
+        <f>SUM(J87:J89,J84)</f>
+        <v>1175.76</v>
+      </c>
       <c r="K86" s="15"/>
-      <c r="L86" s="15"/>
-      <c r="M86" s="15"/>
+      <c r="L86" s="16">
+        <v>305.81</v>
+      </c>
+      <c r="M86" s="16">
+        <v>247.1</v>
+      </c>
       <c r="N86" s="15"/>
-      <c r="O86" s="15"/>
-      <c r="P86" s="15"/>
+      <c r="O86" s="16">
+        <v>371.77</v>
+      </c>
+      <c r="P86" s="17">
+        <v>11.11</v>
+      </c>
       <c r="Q86" s="15"/>
-      <c r="R86" s="15"/>
-      <c r="S86" s="15"/>
-      <c r="T86" s="15"/>
-      <c r="U86" s="15"/>
-      <c r="V86" s="15"/>
-      <c r="W86" s="15"/>
-      <c r="X86" s="15"/>
+      <c r="R86" s="16">
+        <v>226.64</v>
+      </c>
+      <c r="S86" s="16">
+        <v>228.47</v>
+      </c>
+      <c r="T86" s="16">
+        <v>214.42</v>
+      </c>
+      <c r="U86" s="16">
+        <v>195.51</v>
+      </c>
+      <c r="V86" s="17">
+        <v>7.21</v>
+      </c>
+      <c r="W86" s="16">
+        <v>139.72</v>
+      </c>
+      <c r="X86" s="17">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
